--- a/output/pdf_financials_xlsx/EIT.UN.xlsx
+++ b/output/pdf_financials_xlsx/EIT.UN.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/EIT.UN.xlsx
+++ b/output/pdf_financials_xlsx/EIT.UN.xlsx
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2219,7 +2219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3146,7 +3146,11 @@
           <t>Interest Paid</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.003356</v>
       </c>
@@ -5740,6 +5744,132 @@
       </c>
       <c r="F142" s="5" t="n">
         <v>1.141645</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Proceeds from Premium Distribution  and distribution reinvestment plan</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>(Note 6)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" s="5" t="n">
+        <v>0.004537</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.009466</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Proceeds from Premium Distribution  and distribution reinvestment plan</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Amounts paid for repurchase of units (Note 6)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" s="5" t="n">
+        <v>-0.000418</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>-0.013065</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>– from net investment income</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NetInvestmentIncome</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>-0.030346</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>-0.015461</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>– from realized gains on sale of portfolio assets</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>-0.047534</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>– return of capital</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" s="5" t="n">
+        <v>-0.07480100000000001</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>-0.036974</v>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/EIT.UN.xlsx
+++ b/output/pdf_financials_xlsx/EIT.UN.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.014638</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008129000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.020499</v>
+        <v>0.005861</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.144951</v>
+        <v>0.136822</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.020499</v>
+        <v>0.005861</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.144951</v>
+        <v>0.136822</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-208.1750787041738</v>
+        <v>-59.52066619274906</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>111.9399181403969</v>
+        <v>105.6622132983242</v>
       </c>
     </row>
     <row r="31">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
